--- a/oil_prop_database.xlsx
+++ b/oil_prop_database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/85de249484fb506f/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10490492924\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{C2EEF315-D143-4E62-A7C9-832313659139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{159CA1D9-A5FE-4689-81C3-7CC41AE07001}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61CEACE-94D9-4E30-AA33-BDA8AEE89343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B4A1EC41-7C81-440E-920E-F667071639BC}"/>
   </bookViews>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="128">
   <si>
     <t>Density (kg/L)</t>
   </si>
@@ -241,36 +244,6 @@
   </si>
   <si>
     <t>troll blend</t>
-  </si>
-  <si>
-    <t>guyana oil</t>
-  </si>
-  <si>
-    <t>santos light</t>
-  </si>
-  <si>
-    <t>santos medium standard</t>
-  </si>
-  <si>
-    <t>campos med low asph</t>
-  </si>
-  <si>
-    <t>campos med high asph</t>
-  </si>
-  <si>
-    <t>santos med low asph</t>
-  </si>
-  <si>
-    <t>campos med uh asph</t>
-  </si>
-  <si>
-    <t>santos medium ul asph</t>
-  </si>
-  <si>
-    <t>campos heavy standard</t>
-  </si>
-  <si>
-    <t>campos extra heavy</t>
   </si>
   <si>
     <t>gindungo</t>
@@ -496,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -562,6 +535,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -932,8 +908,8 @@
       <c r="B2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>69</v>
+      <c r="C2" s="23">
+        <v>1</v>
       </c>
       <c r="D2" s="5">
         <v>0.85161198106695901</v>
@@ -963,8 +939,8 @@
       <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>70</v>
+      <c r="C3" s="23">
+        <v>2</v>
       </c>
       <c r="D3" s="5">
         <v>0.86365918326010105</v>
@@ -994,8 +970,8 @@
       <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>71</v>
+      <c r="C4" s="23">
+        <v>3</v>
       </c>
       <c r="D4" s="5">
         <v>0.88223925091680899</v>
@@ -1025,8 +1001,8 @@
       <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>72</v>
+      <c r="C5" s="23">
+        <v>4</v>
       </c>
       <c r="D5" s="5">
         <v>0.87146982084390501</v>
@@ -1056,8 +1032,8 @@
       <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>73</v>
+      <c r="C6" s="23">
+        <v>5</v>
       </c>
       <c r="D6" s="5">
         <v>0.88286283141265998</v>
@@ -1087,8 +1063,8 @@
       <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>74</v>
+      <c r="C7" s="23">
+        <v>6</v>
       </c>
       <c r="D7" s="5">
         <v>0.87313183426333296</v>
@@ -1118,8 +1094,8 @@
       <c r="B8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>75</v>
+      <c r="C8" s="23">
+        <v>7</v>
       </c>
       <c r="D8" s="5">
         <v>0.89358644539379495</v>
@@ -1149,8 +1125,8 @@
       <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>76</v>
+      <c r="C9" s="23">
+        <v>8</v>
       </c>
       <c r="D9" s="5">
         <v>0.87478817399604003</v>
@@ -1180,8 +1156,8 @@
       <c r="B10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>77</v>
+      <c r="C10" s="23">
+        <v>9</v>
       </c>
       <c r="D10" s="5">
         <v>0.93724320545601703</v>
@@ -1211,8 +1187,8 @@
       <c r="B11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>78</v>
+      <c r="C11" s="23">
+        <v>10</v>
       </c>
       <c r="D11" s="5">
         <v>0.95161665998789402</v>
@@ -1330,7 +1306,7 @@
         <v>15</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D15" s="15">
         <v>0.9284</v>
@@ -1359,7 +1335,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D16" s="1">
         <v>0.92630000000000001</v>
@@ -1388,7 +1364,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="D17" s="5">
         <v>0.96963670663421697</v>
@@ -1475,7 +1451,7 @@
         <v>9</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D20" s="16">
         <v>0.86135774067374904</v>
@@ -1504,7 +1480,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D21" s="5">
         <v>0.87627861110605298</v>
@@ -1533,7 +1509,7 @@
         <v>9</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D22" s="5">
         <v>0.883388913598392</v>
@@ -1678,7 +1654,7 @@
         <v>15</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D27" s="5">
         <v>0.90600000000000003</v>
@@ -1707,7 +1683,7 @@
         <v>15</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D28" s="5">
         <v>0.91361100534488904</v>
@@ -1736,7 +1712,7 @@
         <v>10</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D29" s="5">
         <v>0.80686923646085096</v>
@@ -1765,7 +1741,7 @@
         <v>10</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D30" s="5">
         <v>0.81102917635974803</v>
@@ -1794,7 +1770,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D31" s="5">
         <v>0.79020219785939805</v>
@@ -1823,7 +1799,7 @@
         <v>10</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D32" s="1">
         <v>0.85050000000000003</v>
@@ -1852,7 +1828,7 @@
         <v>9</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D33" s="1">
         <v>0.88229999999999997</v>
@@ -1939,7 +1915,7 @@
         <v>9</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D36" s="5">
         <v>0.86476783825575398</v>
@@ -1968,7 +1944,7 @@
         <v>9</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D37" s="5">
         <v>0.87304453929203796</v>
@@ -1997,7 +1973,7 @@
         <v>9</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D38" s="5">
         <v>0.84921336609465703</v>
@@ -2664,7 +2640,7 @@
         <v>10</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D61" s="5">
         <v>0.84887273455076895</v>
@@ -2693,7 +2669,7 @@
         <v>10</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D62" s="5">
         <v>0.83790985749807001</v>
@@ -2722,7 +2698,7 @@
         <v>10</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D63" s="10">
         <v>0.819950747237702</v>
@@ -2751,7 +2727,7 @@
         <v>9</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D64" s="5">
         <v>0.88064539040769896</v>
@@ -2780,7 +2756,7 @@
         <v>9</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D65" s="5">
         <v>0.89005051299593896</v>
@@ -2809,7 +2785,7 @@
         <v>15</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D66" s="5">
         <v>0.94660389594334005</v>
@@ -2838,7 +2814,7 @@
         <v>9</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D67" s="5">
         <v>0.85460239749252498</v>
@@ -2867,7 +2843,7 @@
         <v>15</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D68" s="5">
         <v>0.936738476528442</v>
@@ -2896,7 +2872,7 @@
         <v>15</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D69" s="5">
         <v>0.934955822697492</v>
@@ -2954,7 +2930,7 @@
         <v>9</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D71" s="5">
         <v>0.865551193963353</v>
@@ -2983,7 +2959,7 @@
         <v>9</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D72" s="5">
         <v>0.87790433511343602</v>
@@ -3012,7 +2988,7 @@
         <v>9</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D73" s="5">
         <v>0.85459623487388303</v>
@@ -3041,7 +3017,7 @@
         <v>10</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D74" s="5">
         <v>0.76494302072905096</v>
@@ -3070,7 +3046,7 @@
         <v>10</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D75" s="5">
         <v>0.72524524903287702</v>
@@ -3099,7 +3075,7 @@
         <v>10</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D76" s="1">
         <v>0.78439999999999999</v>
@@ -3128,7 +3104,7 @@
         <v>10</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D77" s="5">
         <v>0.829561474809968</v>
@@ -3157,7 +3133,7 @@
         <v>10</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D78" s="5">
         <v>0.84626551080874202</v>
@@ -3186,7 +3162,7 @@
         <v>10</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D79" s="15">
         <v>0.82940000000000003</v>
@@ -3215,7 +3191,7 @@
         <v>10</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D80" s="5">
         <v>0.79781483752652105</v>
@@ -3244,7 +3220,7 @@
         <v>10</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D81" s="5">
         <v>0.69146049518821096</v>
@@ -3273,7 +3249,7 @@
         <v>9</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D82" s="5">
         <v>0.86068287621303097</v>
@@ -3302,7 +3278,7 @@
         <v>10</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D83" s="1">
         <v>0.79859999999999998</v>
@@ -3360,7 +3336,7 @@
         <v>10</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D85" s="1">
         <v>0.7742</v>
@@ -3389,7 +3365,7 @@
         <v>10</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D86" s="1">
         <v>0.83430000000000004</v>
@@ -3418,7 +3394,7 @@
         <v>9</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D87" s="1">
         <v>0.91359999999999997</v>
@@ -3447,7 +3423,7 @@
         <v>9</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D88" s="1">
         <v>0.89980000000000004</v>
@@ -3499,13 +3475,13 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B90" s="8" t="s">
         <v>10</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D90" s="1">
         <v>0.85340000000000005</v>
@@ -3528,13 +3504,13 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B91" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D91" s="5">
         <v>0.91110000000000002</v>
@@ -3557,13 +3533,13 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B92" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D92" s="1">
         <v>0.88549999999999995</v>
@@ -3592,7 +3568,7 @@
         <v>10</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="D93" s="1">
         <v>0.85660000000000003</v>
@@ -3650,7 +3626,7 @@
         <v>10</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D95" s="5">
         <v>0.76805592270304401</v>
@@ -3679,7 +3655,7 @@
         <v>10</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D96" s="5">
         <v>0.79912296395160298</v>
@@ -3708,7 +3684,7 @@
         <v>10</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D97" s="5">
         <v>0.76144437500462903</v>
@@ -3737,7 +3713,7 @@
         <v>9</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D98" s="5">
         <v>0.85929934295270005</v>
@@ -3766,7 +3742,7 @@
         <v>9</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D99" s="16">
         <v>0.874443107326483</v>
@@ -3795,7 +3771,7 @@
         <v>10</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D100" s="1">
         <v>0.72719999999999996</v>
@@ -3847,13 +3823,13 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" s="12" t="s">
         <v>118</v>
-      </c>
-      <c r="B102" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C102" s="12" t="s">
-        <v>128</v>
       </c>
       <c r="D102" s="1">
         <v>0.84289999999999998</v>
@@ -3876,13 +3852,13 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="B103" s="8" t="s">
         <v>10</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D103" s="1">
         <v>0.82469999999999999</v>
@@ -3905,13 +3881,13 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B104" s="8" t="s">
         <v>10</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D104" s="1">
         <v>0.85860000000000003</v>
